--- a/client/src/assets/knowledge/0_coach_knowledge/table_tennis_action_knowledge_v2.xlsx
+++ b/client/src/assets/knowledge/0_coach_knowledge/table_tennis_action_knowledge_v2.xlsx
@@ -3742,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="13.6719" customWidth="1" style="87" min="1" max="1"/>
@@ -3840,6 +3840,16 @@
         </is>
       </c>
       <c r="I4" s="29" t="n"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>动作要领详细说明</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>VIP核心秘诀</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="67" customHeight="1" s="89">
       <c r="A5" s="31" t="inlineStr">
@@ -3879,6 +3889,23 @@
       </c>
       <c r="H5" s="43" t="n"/>
       <c r="I5" s="29" t="n"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **预备**：双脚跨度大，身体重心压低并稍微偏向右侧（右手持拍）。
+- **架肘**：肘部一定要向前架起来，作为发力的稳定支撑点，千万不能贴着肋骨。
+- **内扣**：手腕极度内扣，拍头要能指着自己的腹部，这样才有足够的摩擦空间。
+- **爆发**：击球瞬间前臂带动手腕像拧螺丝一样外展，在最高点通过薄摩擦把球“撕”过去。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>**食指的二次点火发力**：在接触球的那百分之一秒，手腕外展的同时，食指猛地压一下拍肩。这能给球增加一个极强的二次加速度，让球产生“喷射感”。
+**发力方向**：不转球，摩擦住球的顶部后直接往前发力；下旋球，摩擦球的侧后部，弧线够了后也要往前，千万不要继续只往侧上方兜球，否则弧线会过高且球速很慢，毫无威胁。</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="51" customHeight="1" s="89">
       <c r="A6" s="34" t="inlineStr">
@@ -3922,6 +3949,22 @@
         </is>
       </c>
       <c r="I6" s="29" t="n"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **站位**：双脚平行或左脚稍前，身体正对球台，重心稍偏左腿，身体前倾。
+- **引拍**：肘部固定在身体前方不动，前臂自然收至腹前，拍面垂直或稍前倾。引拍时不需要转腰，靠前臂回收即可。
+- **击球**：在来球上升期，前臂以肘关节为轴快速向前方挥出，接触球的中部偏上，以撞击为主。手腕保持稳定，不要乱晃。
+- **还原**：击球后前臂迅速收回至腹前位置。整个动作紧凑快速，幅度控制在前臂长度范围内。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>**肘尖微微上提的"锁肘术"**：拨球前把肘尖稍微抬起来一点，让前臂和球台形成一个微小的向下角度。这样击球时前臂弹出的轨迹自然带一点弧线，球过网后会有明显的"下扎"效果，让对手非常难受。</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="51" customHeight="1" s="89">
       <c r="A7" s="31" t="inlineStr">
@@ -3961,6 +4004,23 @@
       </c>
       <c r="H7" s="43" t="n"/>
       <c r="I7" s="29" t="n"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **站位**：身位稍微偏左（右手持拍），双脚平行或右脚略前，身体重心压在双腿之间，膝盖微曲，身体前倾。
+- **引拍**：腰部微向左转，肘部稍向前顶出，手腕放松内屈，球拍引至腹前偏下方位。
+- **挥拍**：以肘关节为轴，前臂快速向右前方挥动，手腕在接触球瞬间由内屈转为外展，形成由于"鞭打效应"带来的爆发力。
+- **摩擦**：在球的最高点或下降期，接触球的中上部或中部，由下向上、向前方摩擦，使球产生强烈的上旋。
+- **还原**：击球后球拍顺势挥至身体右前方，重心迅速回收，调整步法等待下一次击球。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>**"顶肘弹簧"技术**：反手拉球的动力核心在肘部。引拍时肘部不是缩回来的，而是要微微向外突出（顶肘）。击球瞬间，肘部像一个固定的支点，前臂像被压缩的弹簧一样猛然弹出，这样拉出的球才会有极强的穿透力和旋转。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="53.4" customHeight="1" s="89">
       <c r="A8" s="34" t="inlineStr">
@@ -4000,6 +4060,23 @@
       </c>
       <c r="H8" s="44" t="n"/>
       <c r="I8" s="29" t="n"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>*教练输入：最常用的防御技术，利用反手稳健性控制对手。*
+- **站位**：正对球台或左脚稍前。身体靠近球台，重心略微下沉。
+- **引拍**：几乎不需要引拍，依靠身体重心调节和前臂在腹前的微小迎球动作。拍面根据对方拉球的旋转强度进行显著前倾。
+- **击球**：在来球的上升期击球。手腕固定，以前臂为主去迎球。主要依靠借力和合理的拍面前倾角。
+- **控制**：击球点在身体正前方。接触球的中上部，通过重心的前压来增加控制感。
+- **还原**：由于动作行程极短，击完球后应原地待命或根据落点迅速调整站位。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>**"怀中抱月"的封闭防护**：反手防守时，要把前臂和胸前的空间想象成一个封闭的受控区。球进来时，你的拍子是在这个区域内去等它。千万不要伸手去够球。让球贴近身体击打，不仅能感受到最清晰的手感，还能利用身体躯干的稳定性来抵消对方拉球产生的冲击力。</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="51" customHeight="1" s="89">
       <c r="A9" s="31" t="inlineStr">
@@ -4039,6 +4116,22 @@
       </c>
       <c r="H9" s="43" t="n"/>
       <c r="I9" s="29" t="n"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **站位**：两脚平行站立略比肩宽，重心稍偏右腿，身体离台约40-50cm。
+- **引拍**：以腰带手向右后方小幅度引拍，前臂与大臂夹角约100度，拍面稍前倾。引拍幅度不宜过大，简洁紧凑。
+- **击球**：在来球上升期或最高点击球，击球点在身体右前方。前臂迅速向前挥动，以撞击为主、少量摩擦，接触球的中上部。
+- **收拍**：击球后前臂自然收至眉心位置，迅速还原。整个动作小而快，不要"大力扣杀"式挥拍。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>**食指引导方向的"指哪打哪"**：很多人忽略握拍手食指的作用。攻球瞬间，食指轻轻压住拍面，像瞄准器一样"指"向你要打的落点。这个细节能让你的攻球精度提升一个档次。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="51" customHeight="1" s="89">
       <c r="A10" s="34" t="inlineStr">
@@ -4082,6 +4175,23 @@
         </is>
       </c>
       <c r="I10" s="29" t="n"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **站位**：两脚略比肩宽，左脚稍前（右手持拍），重心落在前脚掌，微微含胸收腹。
+- **引拍**：腰部向右后方转动带动手臂自然引拍，拍面稍前倾，球拍引至身体右侧偏后方，肘部自然弯曲约90度。
+- **蹬转**：击球瞬间右脚蹬地，以腰为轴从右向左转体，带动大臂、前臂、手腕依次发力形成"鞭打效应"。
+- **摩擦**：接触球的中上部，向前上方摩擦为主、撞击为辅，拍面前倾角度根据来球旋转调整。击球点在身体右前方、腰部高度。
+- **还原**：挥拍结束后重心迅速回到中间位，球拍回到身前准备下一板。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>**腰部预紧的"弹簧效应"**：引拍时腰部不是松松垮垮地转过去，而是要有一个"拧紧弹簧"的蓄力感。击球瞬间腰部猛然释放，像弹簧弹开一样，这才是专业选手拉球又快又转的动力核心。</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="51" customHeight="1" s="89">
       <c r="A11" s="31" t="inlineStr">
@@ -4121,6 +4231,23 @@
       </c>
       <c r="H11" s="43" t="n"/>
       <c r="I11" s="29" t="n"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>*教练输入：针对对手强烈拉球的防御技术，注重控制和减力。*
+- **站位**：身体稍微移向球台右侧，两脚稍微开立，重心在前脚掌，身体高度降低，含胸收腹。
+- **引拍**：动作幅度极小，球拍从准备状态微向右方移出，拍面视来球旋转程度进行前倾（通常前倾角度较大）。
+- **击球**：在来球上升期迅速出手。不主动发力挥拍，主要靠借对方的力量。
+- **控球**：接触球的中上部，手腕要保持相对稳定但不要僵硬，通过细微的调节，将球"吸"或"挡"回去。
+- **还原**：击球后迅速回救至准备姿势，重心微调以便连接下一板防御或转攻。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>**"柔中带刚"的柔性阻尼**：把身体想成是汽车的减震器。当对方强力拉球撞击球拍时，手腕、肘部和膝盖要有一个微小的同步缓冲动作，像海绵一样把球的暴冲力吸掉一部分。这种细微的减力控制能让回球落点更短、更低，迫使对手无法连续发力。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="51" customHeight="1" s="89">
       <c r="A12" s="34" t="inlineStr">
@@ -4160,6 +4287,22 @@
       </c>
       <c r="H12" s="44" t="n"/>
       <c r="I12" s="29" t="n"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **抛球**：将球垂直抛起16cm以上（规则要求），抛球手张开不能遮挡。身体放松，重心微沉。
+- **触球角度**：球拍略微放平或稍后仰，用球拍的下半部分（靠近拍头处）接触球的中下部。
+- **摩擦方向**：向前下方快速摩擦，前臂迅速"切"球底部，手腕在触球瞬间有一个急促的加速外展，增加旋转。
+- **假动作**：发球后球拍可以故意做出向前"推送"的虚晃，迷惑对手判断旋转。身体重心保持低姿态，准备第三板抢攻。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>**触球瞬间的"甩腕一抖"**：高手发球旋转强的秘密在于触球那一瞬间手腕的突然加速。整个引拍过程手腕是放松的，在球拍接触球的百分之一秒，手腕猛地一抖，像甩鞭子的末端一样。这个"最后一厘米"的加速才是旋转的灵魂。</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="51" customHeight="1" s="89">
       <c r="A13" s="31" t="inlineStr">
@@ -4199,6 +4342,23 @@
       </c>
       <c r="H13" s="43" t="n"/>
       <c r="I13" s="29" t="n"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **站位**：侧身位站立，双脚距离较宽，左脚在前，身体重心压在左腿上，身体前倾较大。
+- **引拍**：手臂向身体右后方（腋下方向）收拢，手腕下垂并内收，球拍贴近腹部。
+- **击球**：在球下落至略高于球台的位置，由于重心从左脚向右脚稍许回转带动，前臂和手腕迅速向外、向前上方勾击，接触球的中下部或侧下部。
+- **摩擦**：通过手腕爆发力的"勾"式动作，产生强烈的侧上旋或侧下旋。击球点尽量靠近身体中心。
+- **还原**：击球后球拍顺势由左向右挥动后迅速回到准备位置。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>**"腋下藏金"的爆发力**：引拍时，把球拍想成是腋下藏着的一个宝物，要藏得很深。击球瞬间，手腕先做一个向内的小动作，然后猛地向外侧上方弹出。这种"欲扬先抑"的节奏转换是产生迷惑性和高旋转的关键。</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="51" customHeight="1" s="89">
       <c r="A14" s="34" t="inlineStr">
@@ -4238,6 +4398,23 @@
       </c>
       <c r="H14" s="44" t="n"/>
       <c r="I14" s="29" t="n"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>*教练输入：特指张继科、樊振东等运动员常用的发球技术，与普通勾手不同，侧旋转强烈。*
+- **站位**：侧身位站立，双脚与肩同宽或略宽，侧对球台。身体重心较低，双腿微曲。
+- **引拍**：拍头朝下，手臂自然下垂。抛球的同时，前臂内收带动球拍引向腹前，手腕极致内屈，拍面朝向自己。
+- **击球**：在球下落到胸台之间的高度时，前臂迅速由内向外、由后向前挥动。利用手腕由内曲转为外展的爆发力摩擦球的右侧部（以右手为例）。
+- **重心**：击球瞬间中心从右脚转移到左脚，通过腰部的转动带动手臂。
+- **还原**：击球后球拍自然由于惯性挥向身体右前方，随后迅速通过小碎步和身体回转回到中间待球位。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>**"拧腰撇手"的合力技**：逆旋转不仅仅是用手，更要靠腰部的反向扭转。在手腕由内向外撇的同时，腰部做一个向左的猛烈甩动，两股相反的力量汇聚到球拍上，才能发出像职业选手那样具有强烈视觉欺骗性的超强粘性旋转。</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="51" customHeight="1" s="89">
       <c r="A15" s="37" t="inlineStr">
@@ -4277,6 +4454,22 @@
       </c>
       <c r="H15" s="45" t="n"/>
       <c r="I15" s="29" t="n"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **判断**：盯住对方发球触球瞬间的拍面角度和摩擦方向，3步判断法：看触球部位→听击球声音→观球速弧线。
+- **上步**：右脚（右手持拍）迅速跨入台内，脚插到球的正下方，重心跟上去。绝对不能只伸手不动脚！
+- **搓球**：拍面稍后仰，从球的中下部向前下方"切"出去。手腕放松但有控制，用力越轻越好，让球刚过网就往下掉。
+- **摆短**：是搓球的升级版。触球更薄，向下的力量多、向前的力量极少。关键是在球的上升前期就出手，让第一跳落在球网附近。球拍在触球后立刻"刹车"，不往前送。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>**手指松紧交替的"呼吸握拍法"**：搓球和摆短时，引拍阶段手指要"松"——轻轻握住球拍，让拍面有微调的灵活性；触球瞬间手指要"紧"——突然捏紧球拍，把控制力和摩擦力瞬间注入。这个"一松一紧"就像手指在"呼吸"，是台内小球精细控制的终极密码。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="67" customHeight="1" s="89">
       <c r="A16" s="46" t="inlineStr">
@@ -4320,6 +4513,22 @@
         </is>
       </c>
       <c r="I16" s="29" t="n"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **站位**：台内正手位主动进攻技术，右脚迅速上步入台。
+- **引拍**：手腕后展，准备充分。
+- **击球**：在来球弹起的上升期或高点，快速前甩摩擦球中上部，制造突然的快速进攻。重心从后脚蹬到前脚，身体的力量压进台内。
+- **还原**：挑打后迅速退步还原。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>快速上步，找准高点，手腕爆发。</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="51" customHeight="1" s="89">
       <c r="A17" s="49" t="inlineStr">
@@ -4363,6 +4572,22 @@
         </is>
       </c>
       <c r="I17" s="29" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>*教练输入：最精准的技术细节，AI会自动将其转化为视觉检查标准*
+- **站位**：发球准备站位，身体重心平稳。
+- **引拍**：与下旋发球动作相似，以迷惑对手。
+- **击球**：触球时不加摩擦，用拍面撞击球中部推出，制造不转球。
+- **还原**：发球后迅速还原准备下一板。
+---
+###</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>动作似下旋，击球撞中部，碰而不擦。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9495,35 +9720,35 @@
       <c r="I38" s="29" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="87" t="inlineStr">
         <is>
           <t>bh_drive</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="87" t="inlineStr">
         <is>
           <t>bh_drive_intended_loop</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="87" t="inlineStr">
         <is>
           <t>引拍极小、没有蹲腿转腰蓄力，动作幅度偏小</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="87" t="inlineStr">
         <is>
           <t>动作幅度过小，像拨球（针对拉球练习者）</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="87" t="inlineStr">
         <is>
           <t>系统检测到当前的动作更偏向反手拨球。如果你当前的训练目标是『反手拉球』，请注意你的动作幅度太小了：需要增加下蹲蓄力，并加大向上摩擦的幅度，不要仅仅靠前臂去撞击球。</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="87" t="inlineStr">
         <is>
           <t>引拍幅度、蹲腿转腰</t>
         </is>
